--- a/AAII_Financials/Quarterly/HSTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSTO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>HSTO</t>
   </si>
@@ -1697,8 +1697,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-3900</v>
       </c>
       <c r="E23" s="3">
         <v>-2100</v>
@@ -1910,8 +1910,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-3900</v>
       </c>
       <c r="E26" s="3">
         <v>-2100</v>
@@ -1981,8 +1981,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-3900</v>
       </c>
       <c r="E27" s="3">
         <v>-2100</v>
@@ -2407,8 +2407,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-3900</v>
       </c>
       <c r="E33" s="3">
         <v>-2100</v>
@@ -2549,8 +2549,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-3900</v>
       </c>
       <c r="E35" s="3">
         <v>-2100</v>
@@ -5321,8 +5321,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-3900</v>
       </c>
       <c r="E81" s="3">
         <v>-2100</v>
